--- a/4G_Daily_Update.xlsx
+++ b/4G_Daily_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE55898-1BB5-4B2B-9BA2-A6282588E617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BB9EDE-4C71-4C9B-B8F2-AC48F129E020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D7B807F-7D75-4C26-B14A-6863AAF865EE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="197">
   <si>
     <t>Circle</t>
   </si>
@@ -2352,6 +2352,78 @@
   </si>
   <si>
     <t>1. Reselection Time After CSFB Call Idle to LTE (ms): To achieve a faster return time for CSFB MO, please verify that the 2G serving cell belongs to the same site. Additionally, ensure that background download test files are running during the test to facilitate quicker reselection to LTE.</t>
+  </si>
+  <si>
+    <t>HRKNG1_DAV_P47</t>
+  </si>
+  <si>
+    <t>29-Dec-2025 11:23 AM</t>
+  </si>
+  <si>
+    <t>1. PCI
+2. RSRP (Average Value)
+3. SINR (Average Value)
+4. Session establishment time(ms)
+5. Network attach time(ms)
+6. CSFB success rate
+7. CSFB abnormal release rate , drop rate . Mention the cause code of abnormal release
+8. Fast Return Time
+9. VOLTE setup SR</t>
+  </si>
+  <si>
+    <t>1. Static All
+2. Drive DL Ftp
+3. Drive DL Ftp
+4. Static ATDT
+5. Static ATDT
+6. Static CSFB MO
+7. Static CSFB MO
+8. Static CSFB MO
+9. Drive Volte SCMO</t>
+  </si>
+  <si>
+    <t>1. Since the serving cell of the failed sector is different from the recorded PCI, the report is displaying the recorded PCI as the failed sector. Please exclude the current logfile and redo the test with the correct serving PCI.
+2. It appears that the PCI recorded in the site database does not match the actual serving PCI observed on the site, or the failed sector has no corresponding drive data. Request you to please verify the serving cells in the DL drive along with the PCI details in the site database.
+3. It appears that the PCI recorded in the site database does not match the actual serving PCI observed on the site, or the failed sector has no corresponding drive data. Request you to please verify the serving cells in the DL drive along with the PCI details in the site database.
+4. Session Abnormal Release Rate failed due to RLF, poor RF conditions, S1/backhaul instability, handover failures, or hardware issues. Improve RF coverage, verify S1 link, optimize HO parameters, and fix hardware/transport faults to reduce abnormal releases.Exclude ATDT in failed Sector and Redo again.
+5. Verify that the Attach time is within the acceptance criteria. Exclude the ATDT logfile for the failed sector and redo the test. Ensure that a download session is running in the background to achieve a faster attach.
+6. CSFB MO Success Rate failed because the Call Setup Time is above the acceptance criteria, or there are blocked/unsuccessful calls, or fewer than 3 successful calls were completed. Kindly redo the test ensuring CST is within limits and at least 3 MO CSFB calls are successfully established.
+7. There is a call drop in the failed sector. Kindly exclude the affected logfile, create a new logfile, and redo the test to verify successful call completion with no drops.
+8. Reselection Time After CSFB Call Idle to LTE (ms): To achieve a faster return time for CSFB MO, please verify that the 2G serving cell belongs to the same site. Additionally, ensure that background download test files are running during the test to facilitate quicker reselection to LTE.
+9. Add a VoLTE short-call drive across all sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.</t>
+  </si>
+  <si>
+    <t>BENAH1_DAV_P47</t>
+  </si>
+  <si>
+    <t>28-Dec-2025 7:45 AM</t>
+  </si>
+  <si>
+    <t>1. PCI
+2. RSRP (Average Value)
+3. SINR (Average Value)
+4. Session establishment time(ms)
+5. Network Detach Success rate
+6. Fast Return Time
+7. VOLTE setup SR</t>
+  </si>
+  <si>
+    <t>1. Static All
+2. Drive DL Ftp
+3. Drive DL Ftp
+4. Static ATDT
+5. Static Cell Reselection
+6. Static CSFB MO
+7. Drive Volte SCMO</t>
+  </si>
+  <si>
+    <t>1. Since the serving cell of the failed sector is different from the recorded PCI, the report is displaying the recorded PCI as the failed sector. Please exclude the current logfile and redo the test with the correct serving PCI.
+2. It appears that the PCI recorded in the site database does not match the actual serving PCI observed on the site, or the failed sector has no corresponding drive data. Request you to please verify the serving cells in the DL drive along with the PCI details in the site database.
+3. It appears that the PCI recorded in the site database does not match the actual serving PCI observed on the site, or the failed sector has no corresponding drive data. Request you to please verify the serving cells in the DL drive along with the PCI details in the site database.
+4. Session Abnormal Release Rate failed due to RLF, poor RF conditions, S1/backhaul instability, handover failures, or hardware issues. Improve RF coverage, verify S1 link, optimize HO parameters, and fix hardware/transport faults to reduce abnormal releases.Exclude ATDT in failed Sector and Redo again.
+5. Exclude the current logfile and create a new one. Ensure that the Detach Request matches the Detach Accept. Verify this in the Event tab of AZQ before saving the logfile
+6. Reselection Time After CSFB Call Idle to LTE (ms): To achieve a faster return time for CSFB MO, please verify that the 2G serving cell belongs to the same site. Additionally, ensure that background download test files are running during the test to facilitate quicker reselection to LTE.
+7. Add a VoLTE short-call drive across all sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.</t>
   </si>
 </sst>
 </file>
@@ -2835,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D140C61-4D9D-4621-91A9-AB3DA2476B3B}">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.36328125" bestFit="1" customWidth="1"/>
@@ -3938,6 +4010,58 @@
         <v>186</v>
       </c>
     </row>
+    <row r="44" spans="1:8" ht="218.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="171" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/4G_Daily_Update.xlsx
+++ b/4G_Daily_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BB9EDE-4C71-4C9B-B8F2-AC48F129E020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C9C194-0A6F-4253-B165-AC747D12E70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D7B807F-7D75-4C26-B14A-6863AAF865EE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="201">
   <si>
     <t>Circle</t>
   </si>
@@ -2424,6 +2424,33 @@
 5. Exclude the current logfile and create a new one. Ensure that the Detach Request matches the Detach Accept. Verify this in the Event tab of AZQ before saving the logfile
 6. Reselection Time After CSFB Call Idle to LTE (ms): To achieve a faster return time for CSFB MO, please verify that the 2G serving cell belongs to the same site. Additionally, ensure that background download test files are running during the test to facilitate quicker reselection to LTE.
 7. Add a VoLTE short-call drive across all sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.</t>
+  </si>
+  <si>
+    <t>TNKOT1_TUM_P47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. PCI
+2. RSRP (Average Value)
+3. SINR (Average Value)
+4. Session establishment time(ms)
+5. Network Detach Success rate
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Since the serving cell of the failed sector is different from the recorded PCI, the report is displaying the recorded PCI as the failed sector. Please exclude the current logfile and redo the test with the correct serving PCI.
+2. It appears that the PCI recorded in the site database does not match the actual serving PCI observed on the site, or the failed sector has no corresponding drive data. Request you to please verify the serving cells in the DL drive along with the PCI details in the site database.
+3. It appears that the PCI recorded in the site database does not match the actual serving PCI observed on the site, or the failed sector has no corresponding drive data. Request you to please verify the serving cells in the DL drive along with the PCI details in the site database.
+4. Session Abnormal Release Rate failed due to RLF, poor RF conditions, S1/backhaul instability, handover failures, or hardware issues. Improve RF coverage, verify S1 link, optimize HO parameters, and fix hardware/transport faults to reduce abnormal releases.Exclude ATDT in failed Sector and Redo again.
+5. Exclude the current logfile and create a new one. Ensure that the Detach Request matches the Detach Accept. Verify this in the Event tab of AZQ before saving the logfile
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Static All
+2. Drive DL Ftp
+3. Drive DL Ftp
+4. Static ATDT
+5. Static Cell Reselection
+</t>
   </si>
 </sst>
 </file>
@@ -2907,7 +2934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D140C61-4D9D-4621-91A9-AB3DA2476B3B}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.36328125" bestFit="1" customWidth="1"/>
@@ -4062,6 +4089,32 @@
         <v>196</v>
       </c>
     </row>
+    <row r="46" spans="1:8" ht="133" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/4G_Daily_Update.xlsx
+++ b/4G_Daily_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C9C194-0A6F-4253-B165-AC747D12E70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EF9D86-C0E9-4028-8EE1-F88B5DC993E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D7B807F-7D75-4C26-B14A-6863AAF865EE}"/>
   </bookViews>
@@ -3933,7 +3933,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="38" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>9</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="57" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>9</v>
       </c>

--- a/4G_Daily_Update.xlsx
+++ b/4G_Daily_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EF9D86-C0E9-4028-8EE1-F88B5DC993E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B560C4-E309-48F9-BEC7-109D09D6A302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D7B807F-7D75-4C26-B14A-6863AAF865EE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="206">
   <si>
     <t>Circle</t>
   </si>
@@ -2451,6 +2451,27 @@
 4. Static ATDT
 5. Static Cell Reselection
 </t>
+  </si>
+  <si>
+    <t>DAWAR2_BID_P47</t>
+  </si>
+  <si>
+    <t>31-Dec-2025 9:44 AM</t>
+  </si>
+  <si>
+    <t>1. CSFB success rate
+2. Fast Return Time
+3. Check functioning of ViLTE</t>
+  </si>
+  <si>
+    <t>1. Static CSFB MO
+2. Static CSFB MO
+3. Static Video call MO</t>
+  </si>
+  <si>
+    <t>1. CSFB MO Success Rate failed because the Call Setup Time is above the acceptance criteria, or there are blocked/unsuccessful calls, or fewer than 3 successful calls were completed. Kindly redo the test ensuring CST is within limits and at least 3 MO CSFB calls are successfully established.
+2. Reselection Time After CSFB Call Idle to LTE (ms)
+3. Do not use WhatsApp for this test. Perform a manual VoLTE video call after running the script.</t>
   </si>
 </sst>
 </file>
@@ -2934,7 +2955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D140C61-4D9D-4621-91A9-AB3DA2476B3B}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.36328125" bestFit="1" customWidth="1"/>
@@ -4115,6 +4136,32 @@
         <v>199</v>
       </c>
     </row>
+    <row r="47" spans="1:8" ht="47.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>205</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/4G_Daily_Update.xlsx
+++ b/4G_Daily_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B560C4-E309-48F9-BEC7-109D09D6A302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA861F5-1294-4C65-84B7-31D5A7EA0A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D7B807F-7D75-4C26-B14A-6863AAF865EE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="209">
   <si>
     <t>Circle</t>
   </si>
@@ -2472,6 +2472,15 @@
     <t>1. CSFB MO Success Rate failed because the Call Setup Time is above the acceptance criteria, or there are blocked/unsuccessful calls, or fewer than 3 successful calls were completed. Kindly redo the test ensuring CST is within limits and at least 3 MO CSFB calls are successfully established.
 2. Reselection Time After CSFB Call Idle to LTE (ms)
 3. Do not use WhatsApp for this test. Perform a manual VoLTE video call after running the script.</t>
+  </si>
+  <si>
+    <t>KOSAM1_BEN_P47</t>
+  </si>
+  <si>
+    <t>02-Jan-2026 10:20 AM</t>
+  </si>
+  <si>
+    <t>1. Reselection Time After CSFB Call Idle to LTE (ms)</t>
   </si>
 </sst>
 </file>
@@ -2955,7 +2964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D140C61-4D9D-4621-91A9-AB3DA2476B3B}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.36328125" bestFit="1" customWidth="1"/>
@@ -4162,6 +4171,32 @@
         <v>205</v>
       </c>
     </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/4G_Daily_Update.xlsx
+++ b/4G_Daily_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA861F5-1294-4C65-84B7-31D5A7EA0A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B7404A-3E94-4896-AC7F-564C659C49DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D7B807F-7D75-4C26-B14A-6863AAF865EE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="214">
   <si>
     <t>Circle</t>
   </si>
@@ -2481,6 +2481,27 @@
   </si>
   <si>
     <t>1. Reselection Time After CSFB Call Idle to LTE (ms)</t>
+  </si>
+  <si>
+    <t>SALUR1_GUL_P47</t>
+  </si>
+  <si>
+    <t>08-Jan-2026 10:11 AM</t>
+  </si>
+  <si>
+    <t>1. Session establishment time(ms)
+2. Fast Return Time
+3. VOLTE setup SR</t>
+  </si>
+  <si>
+    <t>1. Static ATDT
+2. Static CSFB MO
+3. Drive Volte SCMO</t>
+  </si>
+  <si>
+    <t>1. Session Abnormal Release Rate failed due to RLF, poor RF conditions, S1/backhaul instability, handover failures, or hardware issues. Improve RF coverage, verify S1 link, optimize HO parameters, and fix hardware/transport faults to reduce abnormal releases.Exclude ATDT in failed Sector and Redo again.
+2. Reselection Time After CSFB Call Idle to LTE (ms)
+3. Add a VoLTE short-call drive across all sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.</t>
   </si>
 </sst>
 </file>
@@ -2964,7 +2985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D140C61-4D9D-4621-91A9-AB3DA2476B3B}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.36328125" bestFit="1" customWidth="1"/>
@@ -4197,6 +4218,32 @@
         <v>208</v>
       </c>
     </row>
+    <row r="49" spans="1:8" ht="57" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/4G_Daily_Update.xlsx
+++ b/4G_Daily_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B7404A-3E94-4896-AC7F-564C659C49DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031F764D-C4E3-4648-A747-6F5346E2EA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D7B807F-7D75-4C26-B14A-6863AAF865EE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="212">
   <si>
     <t>Circle</t>
   </si>
@@ -2132,9 +2132,6 @@
     <t>1. Drive Volte SCMO</t>
   </si>
   <si>
-    <t>1. Add a VoLTE short-call drive across all sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.</t>
-  </si>
-  <si>
     <t>11-Dec-2025 11:10 PM</t>
   </si>
   <si>
@@ -2172,9 +2169,6 @@
   <si>
     <t>1. Session Abnormal Release Rate failed due to RLF, poor RF conditions, S1/backhaul instability, handover failures, or hardware issues. Improve RF coverage, verify S1 link, optimize HO parameters, and fix hardware/transport faults to reduce abnormal releases.Exclude ATDT in failed Sector and Redo again.
 2. Exclude the current logfile and create a new one. Ensure that the Detach Request matches the Detach Accept. Verify this in the Event tab of AZQ before saving the logfile</t>
-  </si>
-  <si>
-    <t>HNGRA1_BID_P47</t>
   </si>
   <si>
     <t>864954_GJ_P47</t>
@@ -2267,27 +2261,6 @@
 3. Do not use WhatsApp for this test. Perform a manual VoLTE video call after running the script.</t>
   </si>
   <si>
-    <t xml:space="preserve">
-2. Add a VoLTE short-call drive across all sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.
-3. Do not use WhatsApp for this test. Perform a manual VoLTE video call after running the script.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-2. Drive Volte SCMO
-3. Static Video call MO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-2. VOLTE setup SR
-3. Check functioning of ViLTE</t>
-  </si>
-  <si>
-    <t>SHANK1_HAS_P47</t>
-  </si>
-  <si>
-    <t>DEV001_TUM_P47</t>
-  </si>
-  <si>
     <t>16-Dec-2025 1:25 PM</t>
   </si>
   <si>
@@ -2297,10 +2270,6 @@
   <si>
     <t>1. Drive Volte SCMO
 2. Static Video call MO</t>
-  </si>
-  <si>
-    <t>1. Add a VoLTE short-call drive across all sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.
-2. Do not use WhatsApp for this test. Perform a manual VoLTE video call after running the script.</t>
   </si>
   <si>
     <t>PB</t>
@@ -2426,33 +2395,6 @@
 7. Add a VoLTE short-call drive across all sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.</t>
   </si>
   <si>
-    <t>TNKOT1_TUM_P47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. PCI
-2. RSRP (Average Value)
-3. SINR (Average Value)
-4. Session establishment time(ms)
-5. Network Detach Success rate
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Since the serving cell of the failed sector is different from the recorded PCI, the report is displaying the recorded PCI as the failed sector. Please exclude the current logfile and redo the test with the correct serving PCI.
-2. It appears that the PCI recorded in the site database does not match the actual serving PCI observed on the site, or the failed sector has no corresponding drive data. Request you to please verify the serving cells in the DL drive along with the PCI details in the site database.
-3. It appears that the PCI recorded in the site database does not match the actual serving PCI observed on the site, or the failed sector has no corresponding drive data. Request you to please verify the serving cells in the DL drive along with the PCI details in the site database.
-4. Session Abnormal Release Rate failed due to RLF, poor RF conditions, S1/backhaul instability, handover failures, or hardware issues. Improve RF coverage, verify S1 link, optimize HO parameters, and fix hardware/transport faults to reduce abnormal releases.Exclude ATDT in failed Sector and Redo again.
-5. Exclude the current logfile and create a new one. Ensure that the Detach Request matches the Detach Accept. Verify this in the Event tab of AZQ before saving the logfile
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Static All
-2. Drive DL Ftp
-3. Drive DL Ftp
-4. Static ATDT
-5. Static Cell Reselection
-</t>
-  </si>
-  <si>
     <t>DAWAR2_BID_P47</t>
   </si>
   <si>
@@ -2502,6 +2444,43 @@
     <t>1. Session Abnormal Release Rate failed due to RLF, poor RF conditions, S1/backhaul instability, handover failures, or hardware issues. Improve RF coverage, verify S1 link, optimize HO parameters, and fix hardware/transport faults to reduce abnormal releases.Exclude ATDT in failed Sector and Redo again.
 2. Reselection Time After CSFB Call Idle to LTE (ms)
 3. Add a VoLTE short-call drive across all sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.</t>
+  </si>
+  <si>
+    <t>1. Add a VoLTE short-call drive across Failed sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.</t>
+  </si>
+  <si>
+    <t>863292_GJ_P47</t>
+  </si>
+  <si>
+    <t>12-Dec-2025 1:34 PM</t>
+  </si>
+  <si>
+    <t>1. Add a VoLTE short-call drive across Fail sectors. Do not disconnect the call manually, as it will be counted as a call drop. Each sector must have at least one successful MO session setup.
+2. Do not use WhatsApp for this test. Perform a manual VoLTE video call after running the script.</t>
+  </si>
+  <si>
+    <t>UE</t>
+  </si>
+  <si>
+    <t>JNPR06_JAU_P45</t>
+  </si>
+  <si>
+    <t>10-Jan-2026 6:49 PM</t>
+  </si>
+  <si>
+    <t>1. Network Detach time(ms)
+2. Network Detach Success rate
+3. Check functioning of ViLTE</t>
+  </si>
+  <si>
+    <t>1. Static Cell Reselection
+2. Static Cell Reselection
+3. Static Video call MO</t>
+  </si>
+  <si>
+    <t>1. The Detach Request count is higher than the Detach Accept count. The acceptance criteria require a 100 percent match. Please exclude this logfile, create a new one, and ensure that the Detach Request equals the Detach Accept in the Event tab.
+2. Exclude the current logfile and create a new one. Ensure that the Detach Request matches the Detach Accept. Verify this in the Event tab of AZQ before saving the logfile
+3. Do not use WhatsApp for this test. Perform a manual VoLTE video call after running the script.</t>
   </si>
 </sst>
 </file>
@@ -2635,7 +2614,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2666,9 +2645,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2985,7 +2961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D140C61-4D9D-4621-91A9-AB3DA2476B3B}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.36328125" bestFit="1" customWidth="1"/>
@@ -3773,7 +3749,7 @@
         <v>138</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>139</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="104.5" x14ac:dyDescent="0.35">
@@ -3787,19 +3763,19 @@
         <v>16</v>
       </c>
       <c r="D32" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="4" t="s">
+      <c r="G32" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="H32" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="47.5" x14ac:dyDescent="0.35">
@@ -3813,45 +3789,45 @@
         <v>16</v>
       </c>
       <c r="D33" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="4" t="s">
+      <c r="G33" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="H33" s="10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="142.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:8" ht="114" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="114" x14ac:dyDescent="0.35">
@@ -3859,25 +3835,25 @@
         <v>87</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="4" t="s">
+      <c r="H35" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="218.5" x14ac:dyDescent="0.35">
@@ -3885,25 +3861,25 @@
         <v>9</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G36" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" s="4" t="s">
+      <c r="H36" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="47.5" x14ac:dyDescent="0.35">
@@ -3911,236 +3887,236 @@
         <v>9</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D37" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" s="4" t="s">
+      <c r="H37" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="G37" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="47.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="11">
-        <v>46006.289583333331</v>
+      <c r="D38" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="38" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="19" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>9</v>
+        <v>164</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="11">
-        <v>46006.289583333331</v>
-      </c>
       <c r="E39" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="28.5" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="57" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D40" s="11" t="s">
-        <v>168</v>
+      <c r="D40" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G40" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="19" x14ac:dyDescent="0.35">
-      <c r="A41" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>173</v>
-      </c>
       <c r="C41" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="57" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="218.5" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="28.5" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="171" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="218.5" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="47.5" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="171" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="H45" s="10" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="133" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="57" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>9</v>
       </c>
@@ -4151,97 +4127,71 @@
         <v>16</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>200</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="47.5" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="57" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>9</v>
+        <v>206</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="57" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="57" x14ac:dyDescent="0.35">
-      <c r="A49" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/4G_Daily_Update.xlsx
+++ b/4G_Daily_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031F764D-C4E3-4648-A747-6F5346E2EA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADA0229-6C11-41C4-9B93-050236323860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D7B807F-7D75-4C26-B14A-6863AAF865EE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="212">
   <si>
     <t>Circle</t>
   </si>
@@ -2614,7 +2614,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2645,6 +2645,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2961,7 +2964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D140C61-4D9D-4621-91A9-AB3DA2476B3B}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.36328125" bestFit="1" customWidth="1"/>
@@ -4194,6 +4197,32 @@
         <v>201</v>
       </c>
     </row>
+    <row r="49" spans="1:8" ht="57" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="11">
+        <v>46041.424305555556</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>201</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
